--- a/hw/TMR2615F_osu_pad/nextpcb/CPL-TMR2615F_osu_pad-nextpcb.xlsx
+++ b/hw/TMR2615F_osu_pad/nextpcb/CPL-TMR2615F_osu_pad-nextpcb.xlsx
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>114.2000</v>
+        <v>114.1250</v>
       </c>
       <c r="C23">
-        <v>-102.7000</v>
+        <v>-102.8000</v>
       </c>
       <c r="D23">
         <v>45.0000</v>
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="B87">
-        <v>115.8000</v>
+        <v>116.2000</v>
       </c>
       <c r="C87">
-        <v>-100.4250</v>
+        <v>-100.2500</v>
       </c>
       <c r="D87">
-        <v>-45.0000</v>
+        <v>-90.0000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>87.7050</v>
       </c>
       <c r="C88">
-        <v>-111.4050</v>
+        <v>-111.6300</v>
       </c>
       <c r="D88">
         <v>-90.0000</v>
@@ -2042,7 +2042,7 @@
         <v>90.2000</v>
       </c>
       <c r="C97">
-        <v>-110.9500</v>
+        <v>-111.1750</v>
       </c>
       <c r="D97">
         <v>0.0000</v>
@@ -2770,17 +2770,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">U6</t>
+          <t xml:space="preserve">U7</t>
         </is>
       </c>
       <c r="B132">
-        <v>111.1750</v>
+        <v>120.0250</v>
       </c>
       <c r="C132">
-        <v>-101.5500</v>
+        <v>-94.8750</v>
       </c>
       <c r="D132">
-        <v>180.0000</v>
+        <v>0.0000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -2791,17 +2791,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">U7</t>
+          <t xml:space="preserve">U8</t>
         </is>
       </c>
       <c r="B133">
-        <v>120.0250</v>
+        <v>92.8500</v>
       </c>
       <c r="C133">
-        <v>-94.8750</v>
+        <v>-107.8594</v>
       </c>
       <c r="D133">
-        <v>0.0000</v>
+        <v>-90.0000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -2812,14 +2812,14 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">U8</t>
+          <t xml:space="preserve">U9</t>
         </is>
       </c>
       <c r="B134">
-        <v>93.8500</v>
+        <v>121.7250</v>
       </c>
       <c r="C134">
-        <v>-107.9656</v>
+        <v>-131.9250</v>
       </c>
       <c r="D134">
         <v>90.0000</v>
@@ -2833,17 +2833,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">U9</t>
+          <t xml:space="preserve">U10</t>
         </is>
       </c>
       <c r="B135">
-        <v>121.7250</v>
+        <v>117.7217</v>
       </c>
       <c r="C135">
-        <v>-131.9250</v>
+        <v>-106.9925</v>
       </c>
       <c r="D135">
-        <v>90.0000</v>
+        <v>45.0000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -2854,17 +2854,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">U10</t>
+          <t xml:space="preserve">U11</t>
         </is>
       </c>
       <c r="B136">
-        <v>117.7217</v>
+        <v>127.6500</v>
       </c>
       <c r="C136">
-        <v>-106.9925</v>
+        <v>-107.0000</v>
       </c>
       <c r="D136">
-        <v>45.0000</v>
+        <v>180.0000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -2875,17 +2875,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">U11</t>
+          <t xml:space="preserve">U12</t>
         </is>
       </c>
       <c r="B137">
-        <v>127.6500</v>
+        <v>89.2240</v>
       </c>
       <c r="C137">
-        <v>-107.0000</v>
+        <v>-95.5500</v>
       </c>
       <c r="D137">
-        <v>180.0000</v>
+        <v>-90.0000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -2896,17 +2896,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">U12</t>
+          <t xml:space="preserve">U13</t>
         </is>
       </c>
       <c r="B138">
-        <v>89.2240</v>
+        <v>90.9600</v>
       </c>
       <c r="C138">
-        <v>-95.5500</v>
+        <v>-120.9500</v>
       </c>
       <c r="D138">
-        <v>-90.0000</v>
+        <v>180.0000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -2917,17 +2917,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">U13</t>
+          <t xml:space="preserve">U14</t>
         </is>
       </c>
       <c r="B139">
-        <v>90.9600</v>
+        <v>94.0500</v>
       </c>
       <c r="C139">
-        <v>-120.9500</v>
+        <v>-126.0300</v>
       </c>
       <c r="D139">
-        <v>180.0000</v>
+        <v>0.0000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -2938,17 +2938,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">U14</t>
+          <t xml:space="preserve">U15</t>
         </is>
       </c>
       <c r="B140">
-        <v>94.0500</v>
+        <v>110.0100</v>
       </c>
       <c r="C140">
-        <v>-126.0300</v>
+        <v>-120.9500</v>
       </c>
       <c r="D140">
-        <v>0.0000</v>
+        <v>180.0000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -2959,17 +2959,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">U15</t>
+          <t xml:space="preserve">U16</t>
         </is>
       </c>
       <c r="B141">
-        <v>110.0100</v>
+        <v>113.1000</v>
       </c>
       <c r="C141">
-        <v>-120.9500</v>
+        <v>-126.0300</v>
       </c>
       <c r="D141">
-        <v>180.0000</v>
+        <v>0.0000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -2980,17 +2980,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">U16</t>
+          <t xml:space="preserve">U17</t>
         </is>
       </c>
       <c r="B142">
-        <v>113.1000</v>
+        <v>129.0600</v>
       </c>
       <c r="C142">
-        <v>-126.0300</v>
+        <v>-120.9500</v>
       </c>
       <c r="D142">
-        <v>0.0000</v>
+        <v>180.0000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3001,17 +3001,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">U17</t>
+          <t xml:space="preserve">U18</t>
         </is>
       </c>
       <c r="B143">
-        <v>129.0600</v>
+        <v>132.1500</v>
       </c>
       <c r="C143">
-        <v>-120.9500</v>
+        <v>-126.0300</v>
       </c>
       <c r="D143">
-        <v>180.0000</v>
+        <v>0.0000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -3022,17 +3022,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">U18</t>
+          <t xml:space="preserve">U19</t>
         </is>
       </c>
       <c r="B144">
-        <v>132.1500</v>
+        <v>90.9600</v>
       </c>
       <c r="C144">
-        <v>-126.0300</v>
+        <v>-140.0000</v>
       </c>
       <c r="D144">
-        <v>0.0000</v>
+        <v>180.0000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -3043,17 +3043,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">U19</t>
+          <t xml:space="preserve">U20</t>
         </is>
       </c>
       <c r="B145">
-        <v>90.9600</v>
+        <v>94.0500</v>
       </c>
       <c r="C145">
-        <v>-140.0000</v>
+        <v>-145.0800</v>
       </c>
       <c r="D145">
-        <v>180.0000</v>
+        <v>0.0000</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -3064,17 +3064,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">U20</t>
+          <t xml:space="preserve">U21</t>
         </is>
       </c>
       <c r="B146">
-        <v>94.0500</v>
+        <v>110.0100</v>
       </c>
       <c r="C146">
-        <v>-145.0800</v>
+        <v>-140.0000</v>
       </c>
       <c r="D146">
-        <v>0.0000</v>
+        <v>180.0000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -3085,17 +3085,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">U21</t>
+          <t xml:space="preserve">U22</t>
         </is>
       </c>
       <c r="B147">
-        <v>110.0100</v>
+        <v>113.1000</v>
       </c>
       <c r="C147">
-        <v>-140.0000</v>
+        <v>-145.0800</v>
       </c>
       <c r="D147">
-        <v>180.0000</v>
+        <v>0.0000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -3106,17 +3106,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">U22</t>
+          <t xml:space="preserve">U23</t>
         </is>
       </c>
       <c r="B148">
-        <v>113.1000</v>
+        <v>129.0600</v>
       </c>
       <c r="C148">
-        <v>-145.0800</v>
+        <v>-140.0000</v>
       </c>
       <c r="D148">
-        <v>0.0000</v>
+        <v>180.0000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -3127,17 +3127,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">U23</t>
+          <t xml:space="preserve">U24</t>
         </is>
       </c>
       <c r="B149">
-        <v>129.0600</v>
+        <v>132.1500</v>
       </c>
       <c r="C149">
-        <v>-140.0000</v>
+        <v>-145.0800</v>
       </c>
       <c r="D149">
-        <v>180.0000</v>
+        <v>0.0000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -3148,14 +3148,14 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">U24</t>
+          <t xml:space="preserve">U25</t>
         </is>
       </c>
       <c r="B150">
-        <v>132.1500</v>
+        <v>112.0750</v>
       </c>
       <c r="C150">
-        <v>-145.0800</v>
+        <v>-98.9000</v>
       </c>
       <c r="D150">
         <v>0.0000</v>
@@ -3169,19 +3169,40 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t xml:space="preserve">U26</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>113.2750</v>
+      </c>
+      <c r="C151">
+        <v>-98.9000</v>
+      </c>
+      <c r="D151">
+        <v>180.0000</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
           <t xml:space="preserve">X1</t>
         </is>
       </c>
-      <c r="B151">
+      <c r="B152">
         <v>121.8217</v>
       </c>
-      <c r="C151">
+      <c r="C152">
         <v>-113.3902</v>
       </c>
-      <c r="D151">
+      <c r="D152">
         <v>45.0000</v>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t xml:space="preserve">Top</t>
         </is>
